--- a/ms_tables/tableS5_mantel_tests_n4_E_large_fam.xlsx
+++ b/ms_tables/tableS5_mantel_tests_n4_E_large_fam.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/ms_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BB3C4E-FB74-8347-A215-D645436F4FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C30BDC3-F5F1-DD44-AFC8-18227F36055E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -568,19 +568,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>960119</xdr:colOff>
+      <xdr:colOff>969496</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1960</xdr:rowOff>
+      <xdr:rowOff>7543</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE920D1-CAE8-C248-A843-2E70EB81B74A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED72D0AA-B45B-964B-9EFD-6F78CAE2EE90}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -588,7 +588,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4780279" y="205160"/>
+              <a:off x="4808804" y="212697"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -654,7 +654,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -712,7 +712,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -726,13 +726,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE920D1-CAE8-C248-A843-2E70EB81B74A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED72D0AA-B45B-964B-9EFD-6F78CAE2EE90}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -740,7 +740,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4780279" y="205160"/>
+              <a:off x="4808804" y="212697"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -779,37 +779,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -822,19 +822,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>772161</xdr:colOff>
+      <xdr:colOff>781538</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>5583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F464CD6-DE39-F648-AA21-A26DE00F348E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F912DB5-98DD-A846-9358-6639C8D2600F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -842,7 +842,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2692401" y="203200"/>
+              <a:off x="2706076" y="210737"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -877,6 +877,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -908,73 +966,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F464CD6-DE39-F648-AA21-A26DE00F348E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F912DB5-98DD-A846-9358-6639C8D2600F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -982,7 +988,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2692401" y="203200"/>
+              <a:off x="2706076" y="210737"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1012,9 +1018,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1023,25 +1059,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1052,19 +1070,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>993089</xdr:colOff>
+      <xdr:colOff>984323</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>2583</xdr:rowOff>
+      <xdr:rowOff>8166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EACE18FB-9217-7341-856B-306EC52F73BB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4A12C5-6FB0-C24F-BBCD-31DE9787A136}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1072,7 +1090,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3736289" y="205783"/>
+              <a:off x="3739246" y="213320"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1204,13 +1222,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EACE18FB-9217-7341-856B-306EC52F73BB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4A12C5-6FB0-C24F-BBCD-31DE9787A136}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1218,7 +1236,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3736289" y="205783"/>
+              <a:off x="3739246" y="213320"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1300,19 +1318,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>939799</xdr:colOff>
+      <xdr:colOff>952441</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1960</xdr:rowOff>
+      <xdr:rowOff>7543</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C88009FD-AB9A-9040-B464-CE952E33B567}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73F7092-8EEA-2448-8301-A181F6628715}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1320,7 +1338,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8346439" y="205160"/>
+              <a:off x="8396595" y="212697"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1386,7 +1404,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1444,7 +1462,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1458,13 +1476,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C88009FD-AB9A-9040-B464-CE952E33B567}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73F7092-8EEA-2448-8301-A181F6628715}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1472,7 +1490,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8346439" y="205160"/>
+              <a:off x="8396595" y="212697"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1511,37 +1529,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1554,19 +1572,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1361441</xdr:colOff>
+      <xdr:colOff>1383155</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9358CB3-6F50-8649-B0CC-6974B50FF5F4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DA21269-A42C-0441-87EE-1F73FBA5F8D0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1574,7 +1592,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6258561" y="203200"/>
+              <a:off x="6306847" y="205154"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1609,6 +1627,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1640,73 +1716,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9358CB3-6F50-8649-B0CC-6974B50FF5F4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DA21269-A42C-0441-87EE-1F73FBA5F8D0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1714,7 +1738,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6258561" y="203200"/>
+              <a:off x="6306847" y="205154"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1744,9 +1768,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1755,25 +1809,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1784,19 +1820,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>972769</xdr:colOff>
+      <xdr:colOff>985411</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>2583</xdr:rowOff>
+      <xdr:rowOff>8166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33A34EEB-7E95-DB49-9415-527E92205DBC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F6046DB-9C44-244B-92F1-9F5A0A12E2EB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1804,7 +1840,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7302449" y="205783"/>
+              <a:off x="7345180" y="213320"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1936,13 +1972,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33A34EEB-7E95-DB49-9415-527E92205DBC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F6046DB-9C44-244B-92F1-9F5A0A12E2EB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1950,7 +1986,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7302449" y="205783"/>
+              <a:off x="7345180" y="213320"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2032,19 +2068,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>939799</xdr:colOff>
+      <xdr:colOff>979656</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1960</xdr:rowOff>
+      <xdr:rowOff>7544</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="662579" cy="215754"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33188983-62F5-E14D-B838-02B55E7913C0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4AAD7D7-2D5A-DF46-9916-9C2C67888B91}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2052,8 +2088,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11902439" y="205160"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="11979810" y="212698"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2118,7 +2154,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2176,7 +2212,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2190,13 +2226,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33188983-62F5-E14D-B838-02B55E7913C0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4AAD7D7-2D5A-DF46-9916-9C2C67888B91}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2204,8 +2240,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11902439" y="205160"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="11979810" y="212698"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2243,37 +2279,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -2286,19 +2322,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1341121</xdr:colOff>
+      <xdr:colOff>1362835</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F42EED42-85D0-6747-9A50-AA9886F90B12}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5F80F9A-9F75-634B-B33D-E660D7689ABB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2306,7 +2342,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9814561" y="203200"/>
+              <a:off x="9871835" y="205154"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2341,6 +2377,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2372,73 +2466,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F42EED42-85D0-6747-9A50-AA9886F90B12}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5F80F9A-9F75-634B-B33D-E660D7689ABB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2446,7 +2488,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9814561" y="203200"/>
+              <a:off x="9871835" y="205154"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2476,9 +2518,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2487,25 +2559,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2516,19 +2570,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>972769</xdr:colOff>
+      <xdr:colOff>1012626</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>2583</xdr:rowOff>
+      <xdr:rowOff>8167</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="662579" cy="215754"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{295AF59A-2015-764F-A156-BF6DE8CB2729}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349DA9BC-A47A-1F40-B781-05B0359366E9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2536,8 +2590,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10858449" y="205783"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="10928395" y="213321"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2668,13 +2722,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{295AF59A-2015-764F-A156-BF6DE8CB2729}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349DA9BC-A47A-1F40-B781-05B0359366E9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2682,8 +2736,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10858449" y="205783"/>
-              <a:ext cx="707834" cy="181231"/>
+              <a:off x="10928395" y="213321"/>
+              <a:ext cx="662579" cy="215754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
